--- a/LAFExamples/analysis/trolley_problem-scores-trust.xlsx
+++ b/LAFExamples/analysis/trolley_problem-scores-trust.xlsx
@@ -26,28 +26,28 @@
     <t>#Arg-</t>
   </si>
   <si>
-    <t>L4: Actively choosing inaction is a form of intervention</t>
-  </si>
-  <si>
-    <t>L1: Pull the Lever, killing one person</t>
-  </si>
-  <si>
-    <t>L6: Do Nothing, killing 5 people</t>
-  </si>
-  <si>
-    <t>L2: active intervention means taking moral responsibility</t>
-  </si>
-  <si>
-    <t>L0: prioritizing the greater good is a slippery slope</t>
-  </si>
-  <si>
-    <t>L3: all lives are of equal moral worth</t>
-  </si>
-  <si>
-    <t>L7: Maximizing the greater good</t>
-  </si>
-  <si>
-    <t>L5: Moral obligation to help  and take action</t>
+    <t>L7: Actively choosing inaction is a form of intervention</t>
+  </si>
+  <si>
+    <t>L3: Pull the Lever, killing one person</t>
+  </si>
+  <si>
+    <t>L0: Do Nothing, killing 5 people</t>
+  </si>
+  <si>
+    <t>L1: active intervention means taking moral responsibility</t>
+  </si>
+  <si>
+    <t>L2: prioritizing the greater good is a slippery slope</t>
+  </si>
+  <si>
+    <t>L5: all lives are of equal moral worth</t>
+  </si>
+  <si>
+    <t>L4: Maximizing the greater good</t>
+  </si>
+  <si>
+    <t>L6: Moral obligation to help  and take action</t>
   </si>
   <si>
     <t>Undercuts</t>
@@ -62,6 +62,12 @@
     <t>logAccumulator</t>
   </si>
   <si>
+    <t>[1.0, 1.0, 1.0]</t>
+  </si>
+  <si>
+    <t>[1.0, 0.5]</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
@@ -72,12 +78,6 @@
   </si>
   <si>
     <t>[1.0]</t>
-  </si>
-  <si>
-    <t>[1.0, 1.0, 1.0]</t>
-  </si>
-  <si>
-    <t>[1.0, 0.5]</t>
   </si>
   <si>
     <t>Rebuttals</t>
@@ -446,16 +446,16 @@
         <v>0.0</v>
       </c>
       <c r="E3" t="s" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n" s="5">
         <v>0.6931471824645996</v>
       </c>
       <c r="H3" t="s" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>25</v>
@@ -478,10 +478,10 @@
         <v>2.0</v>
       </c>
       <c r="E4" t="s" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n" s="5">
         <v>0.15415067970752716</v>
@@ -510,10 +510,10 @@
         <v>2.0</v>
       </c>
       <c r="E5" t="s" s="15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n" s="5">
         <v>0.4700036346912384</v>
@@ -542,19 +542,19 @@
         <v>0.0</v>
       </c>
       <c r="E6" t="s" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G6" t="n" s="7">
         <v>0.0</v>
       </c>
       <c r="H6" t="s" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J6" t="n" s="7">
         <v>0.0</v>
@@ -574,19 +574,19 @@
         <v>0.0</v>
       </c>
       <c r="E7" t="s" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n" s="7">
         <v>0.0</v>
       </c>
       <c r="H7" t="s" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J7" t="n" s="7">
         <v>0.0</v>
@@ -606,19 +606,19 @@
         <v>0.0</v>
       </c>
       <c r="E8" t="s" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n" s="7">
         <v>0.0</v>
       </c>
       <c r="H8" t="s" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J8" t="n" s="7">
         <v>0.0</v>
@@ -638,10 +638,10 @@
         <v>1.0</v>
       </c>
       <c r="E9" t="s" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n" s="6">
         <v>-0.6931471824645996</v>
@@ -650,7 +650,7 @@
         <v>25</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J9" t="n" s="6">
         <v>-0.28768208622932434</v>
@@ -670,19 +670,19 @@
         <v>0.0</v>
       </c>
       <c r="E10" t="s" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n" s="7">
         <v>0.0</v>
       </c>
       <c r="H10" t="s" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J10" t="n" s="7">
         <v>0.0</v>

--- a/LAFExamples/analysis/trolley_problem-scores-trust.xlsx
+++ b/LAFExamples/analysis/trolley_problem-scores-trust.xlsx
@@ -26,28 +26,28 @@
     <t>#Arg-</t>
   </si>
   <si>
-    <t>L7: Actively choosing inaction is a form of intervention</t>
-  </si>
-  <si>
-    <t>L3: Pull the Lever, killing one person</t>
-  </si>
-  <si>
-    <t>L0: Do Nothing, killing 5 people</t>
-  </si>
-  <si>
-    <t>L1: active intervention means taking moral responsibility</t>
-  </si>
-  <si>
-    <t>L2: prioritizing the greater good is a slippery slope</t>
-  </si>
-  <si>
-    <t>L5: all lives are of equal moral worth</t>
-  </si>
-  <si>
-    <t>L4: Maximizing the greater good</t>
-  </si>
-  <si>
-    <t>L6: Moral obligation to help  and take action</t>
+    <t>L0: Actively choosing inaction is a form of intervention</t>
+  </si>
+  <si>
+    <t>L1: Pull the Lever, killing one person</t>
+  </si>
+  <si>
+    <t>L2: Do Nothing, killing 5 people</t>
+  </si>
+  <si>
+    <t>L5: active intervention means taking moral responsibility</t>
+  </si>
+  <si>
+    <t>L4: prioritizing the greater good is a slippery slope</t>
+  </si>
+  <si>
+    <t>L6: all lives are of equal moral worth</t>
+  </si>
+  <si>
+    <t>L3: Maximizing the greater good</t>
+  </si>
+  <si>
+    <t>L7: Moral obligation to help  and take action</t>
   </si>
   <si>
     <t>Undercuts</t>
@@ -62,34 +62,34 @@
     <t>logAccumulator</t>
   </si>
   <si>
+    <t>[1.0]</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1.0, 0.5, 1.0]</t>
+  </si>
+  <si>
+    <t>[1.0, 1.0]</t>
+  </si>
+  <si>
     <t>[1.0, 1.0, 1.0]</t>
   </si>
   <si>
     <t>[1.0, 0.5]</t>
   </si>
   <si>
-    <t>[]</t>
-  </si>
-  <si>
-    <t>[1.0, 0.5, 1.0]</t>
-  </si>
-  <si>
-    <t>[1.0, 1.0]</t>
-  </si>
-  <si>
-    <t>[1.0]</t>
-  </si>
-  <si>
     <t>Rebuttals</t>
   </si>
   <si>
+    <t>[0.5]</t>
+  </si>
+  <si>
     <t>[0.33333334]</t>
   </si>
   <si>
     <t>[0.25]</t>
-  </si>
-  <si>
-    <t>[0.5]</t>
   </si>
 </sst>
 </file>
@@ -446,19 +446,19 @@
         <v>0.0</v>
       </c>
       <c r="E3" t="s" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n" s="5">
         <v>0.6931471824645996</v>
       </c>
       <c r="H3" t="s" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n" s="5">
         <v>0.28768208622932434</v>
@@ -478,19 +478,19 @@
         <v>2.0</v>
       </c>
       <c r="E4" t="s" s="15">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s" s="0">
         <v>19</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>20</v>
       </c>
       <c r="G4" t="n" s="5">
         <v>0.15415067970752716</v>
       </c>
       <c r="H4" t="s" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n" s="5">
         <v>0.06453855335712433</v>
@@ -510,19 +510,19 @@
         <v>2.0</v>
       </c>
       <c r="E5" t="s" s="15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n" s="5">
         <v>0.4700036346912384</v>
       </c>
       <c r="H5" t="s" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J5" t="n" s="5">
         <v>0.06453855335712433</v>
@@ -542,19 +542,19 @@
         <v>0.0</v>
       </c>
       <c r="E6" t="s" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n" s="7">
         <v>0.0</v>
       </c>
       <c r="H6" t="s" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J6" t="n" s="7">
         <v>0.0</v>
@@ -574,19 +574,19 @@
         <v>0.0</v>
       </c>
       <c r="E7" t="s" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" t="n" s="7">
         <v>0.0</v>
       </c>
       <c r="H7" t="s" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J7" t="n" s="7">
         <v>0.0</v>
@@ -606,19 +606,19 @@
         <v>0.0</v>
       </c>
       <c r="E8" t="s" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n" s="7">
         <v>0.0</v>
       </c>
       <c r="H8" t="s" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n" s="7">
         <v>0.0</v>
@@ -638,19 +638,19 @@
         <v>1.0</v>
       </c>
       <c r="E9" t="s" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n" s="6">
         <v>-0.6931471824645996</v>
       </c>
       <c r="H9" t="s" s="15">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J9" t="n" s="6">
         <v>-0.28768208622932434</v>
@@ -670,19 +670,19 @@
         <v>0.0</v>
       </c>
       <c r="E10" t="s" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G10" t="n" s="7">
         <v>0.0</v>
       </c>
       <c r="H10" t="s" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J10" t="n" s="7">
         <v>0.0</v>
